--- a/public/Daywise_Distance_April_2026.xlsx
+++ b/public/Daywise_Distance_April_2026.xlsx
@@ -911,7 +911,7 @@
         <v>37</v>
       </c>
       <c r="D4" s="3">
-        <v>1255</v>
+        <v>1337</v>
       </c>
       <c r="E4" s="3">
         <v>41</v>
@@ -1116,6 +1116,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>